--- a/src/data/raw/დამფუძნებელი კრება, 1919.xlsx
+++ b/src/data/raw/დამფუძნებელი კრება, 1919.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBEBE46-33DE-4694-BD86-9B74999B48F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="6" r:id="rId1"/>
